--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321045</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321045</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129321045</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,619 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129809725</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91613</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Granticka 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>473713</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6816382</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129809713</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>473665</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6816140</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129809779</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80215</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stuplav sotbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>473743</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6816448</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129809703</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett 1, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>473665</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6816140</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129809770</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tretå 2 Sotbo , Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>473875</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6816623</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129809630</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58369</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tallbit, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>473785</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6816297</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,27 +1208,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809770</v>
+        <v>129809630</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>58369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1237,24 +1237,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tretå 2 Sotbo , Dlr</t>
+          <t>Tallbit, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473875</v>
+        <v>473785</v>
       </c>
       <c r="R7" t="n">
-        <v>6816623</v>
+        <v>6816297</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,27 +1305,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809630</v>
+        <v>129809770</v>
       </c>
       <c r="B8" t="n">
-        <v>58369</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1344,19 +1334,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tallbit, Dlr</t>
+          <t>Tretå 2 Sotbo , Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473785</v>
+        <v>473875</v>
       </c>
       <c r="R8" t="n">
-        <v>6816297</v>
+        <v>6816623</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,6 +1381,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,6 +1409,123 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129820910</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91835</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5260</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lateritticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Postia lateritia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Renvall</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lateritticka Sotbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>473772</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6816315</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre tallåga</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129809725</v>
       </c>
       <c r="B3" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1208,27 +1208,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809630</v>
+        <v>129809770</v>
       </c>
       <c r="B7" t="n">
-        <v>58369</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1237,19 +1237,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallbit, Dlr</t>
+          <t>Tretå 2 Sotbo , Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473785</v>
+        <v>473875</v>
       </c>
       <c r="R7" t="n">
-        <v>6816297</v>
+        <v>6816623</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,6 +1284,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,27 +1315,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809770</v>
+        <v>129809630</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>58369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1334,24 +1344,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tretå 2 Sotbo , Dlr</t>
+          <t>Tallbit, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473875</v>
+        <v>473785</v>
       </c>
       <c r="R8" t="n">
-        <v>6816623</v>
+        <v>6816297</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,11 +1386,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1415,7 @@
         <v>129820910</v>
       </c>
       <c r="B9" t="n">
-        <v>91835</v>
+        <v>91839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129809725</v>
       </c>
       <c r="B3" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1208,27 +1208,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809770</v>
+        <v>129809630</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>58369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1237,24 +1237,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tretå 2 Sotbo , Dlr</t>
+          <t>Tallbit, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473875</v>
+        <v>473785</v>
       </c>
       <c r="R7" t="n">
-        <v>6816623</v>
+        <v>6816297</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,27 +1305,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809630</v>
+        <v>129809770</v>
       </c>
       <c r="B8" t="n">
-        <v>58369</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1344,19 +1334,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tallbit, Dlr</t>
+          <t>Tretå 2 Sotbo , Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473785</v>
+        <v>473875</v>
       </c>
       <c r="R8" t="n">
-        <v>6816297</v>
+        <v>6816623</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,6 +1381,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1415,7 @@
         <v>129820910</v>
       </c>
       <c r="B9" t="n">
-        <v>91839</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -1208,27 +1208,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809630</v>
+        <v>129809770</v>
       </c>
       <c r="B7" t="n">
-        <v>58369</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1237,19 +1237,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallbit, Dlr</t>
+          <t>Tretå 2 Sotbo , Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473785</v>
+        <v>473875</v>
       </c>
       <c r="R7" t="n">
-        <v>6816297</v>
+        <v>6816623</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,6 +1284,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,27 +1315,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809770</v>
+        <v>129809630</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>58369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1334,24 +1344,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tretå 2 Sotbo , Dlr</t>
+          <t>Tallbit, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473875</v>
+        <v>473785</v>
       </c>
       <c r="R8" t="n">
-        <v>6816623</v>
+        <v>6816297</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,11 +1386,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -892,48 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809713</v>
+        <v>129809779</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett 1, Dlr</t>
+          <t>Stuplav sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473665</v>
+        <v>473743</v>
       </c>
       <c r="R4" t="n">
-        <v>6816140</v>
+        <v>6816448</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,6 +973,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -989,48 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809779</v>
+        <v>129809713</v>
       </c>
       <c r="B5" t="n">
-        <v>80215</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stuplav sotbo, Dlr</t>
+          <t>Tretåig hackspett 1, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473743</v>
+        <v>473665</v>
       </c>
       <c r="R5" t="n">
-        <v>6816448</v>
+        <v>6816140</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,21 +1085,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129809725</v>
       </c>
       <c r="B3" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,48 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809779</v>
+        <v>129809713</v>
       </c>
       <c r="B4" t="n">
-        <v>80215</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stuplav sotbo, Dlr</t>
+          <t>Tretåig hackspett 1, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473743</v>
+        <v>473665</v>
       </c>
       <c r="R4" t="n">
-        <v>6816448</v>
+        <v>6816140</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,21 +973,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1004,48 +989,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809713</v>
+        <v>129809779</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>80218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett 1, Dlr</t>
+          <t>Stuplav sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473665</v>
+        <v>473743</v>
       </c>
       <c r="R5" t="n">
-        <v>6816140</v>
+        <v>6816448</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,6 +1070,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1104,7 +1104,7 @@
         <v>129809703</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,27 +1208,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809770</v>
+        <v>129809630</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>58372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1237,24 +1237,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tretå 2 Sotbo , Dlr</t>
+          <t>Tallbit, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473875</v>
+        <v>473785</v>
       </c>
       <c r="R7" t="n">
-        <v>6816623</v>
+        <v>6816297</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,27 +1305,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809630</v>
+        <v>129809770</v>
       </c>
       <c r="B8" t="n">
-        <v>58369</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1344,19 +1334,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tallbit, Dlr</t>
+          <t>Tretå 2 Sotbo , Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473785</v>
+        <v>473875</v>
       </c>
       <c r="R8" t="n">
-        <v>6816297</v>
+        <v>6816623</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,6 +1381,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1415,7 @@
         <v>129820910</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129809725</v>
       </c>
       <c r="B3" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,48 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809713</v>
+        <v>129809779</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett 1, Dlr</t>
+          <t>Stuplav sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473665</v>
+        <v>473743</v>
       </c>
       <c r="R4" t="n">
-        <v>6816140</v>
+        <v>6816448</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,6 +973,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -989,48 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809779</v>
+        <v>129809713</v>
       </c>
       <c r="B5" t="n">
-        <v>80218</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stuplav sotbo, Dlr</t>
+          <t>Tretåig hackspett 1, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473743</v>
+        <v>473665</v>
       </c>
       <c r="R5" t="n">
-        <v>6816448</v>
+        <v>6816140</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,21 +1085,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1104,7 +1104,7 @@
         <v>129809703</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,27 +1208,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809630</v>
+        <v>129809770</v>
       </c>
       <c r="B7" t="n">
-        <v>58372</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1237,19 +1237,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tallbit, Dlr</t>
+          <t>Tretå 2 Sotbo , Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473785</v>
+        <v>473875</v>
       </c>
       <c r="R7" t="n">
-        <v>6816297</v>
+        <v>6816623</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1279,6 +1284,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,27 +1315,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809770</v>
+        <v>129809630</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>58375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1334,24 +1344,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tretå 2 Sotbo , Dlr</t>
+          <t>Tallbit, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473875</v>
+        <v>473785</v>
       </c>
       <c r="R8" t="n">
-        <v>6816623</v>
+        <v>6816297</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1381,11 +1386,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,7 +1415,7 @@
         <v>129820910</v>
       </c>
       <c r="B9" t="n">
-        <v>91844</v>
+        <v>91847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1410,123 +1410,6 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>129820910</v>
-      </c>
-      <c r="B9" t="n">
-        <v>91847</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5260</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lateritticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Postia lateritia</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Renvall</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Lateritticka Sotbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>473772</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6816315</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre tallåga</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129809725</v>
       </c>
       <c r="B3" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129809779</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>129809713</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129809725</v>
       </c>
       <c r="B3" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,48 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809779</v>
+        <v>129809713</v>
       </c>
       <c r="B4" t="n">
-        <v>80222</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stuplav sotbo, Dlr</t>
+          <t>Tretåig hackspett 1, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473743</v>
+        <v>473665</v>
       </c>
       <c r="R4" t="n">
-        <v>6816448</v>
+        <v>6816140</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,21 +973,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1004,48 +989,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809713</v>
+        <v>129809779</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>80223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett 1, Dlr</t>
+          <t>Stuplav sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473665</v>
+        <v>473743</v>
       </c>
       <c r="R5" t="n">
-        <v>6816140</v>
+        <v>6816448</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,6 +1070,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1318,7 +1318,7 @@
         <v>129809630</v>
       </c>
       <c r="B8" t="n">
-        <v>58375</v>
+        <v>58376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129809725</v>
       </c>
       <c r="B3" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,48 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809713</v>
+        <v>129809779</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett 1, Dlr</t>
+          <t>Stuplav sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473665</v>
+        <v>473743</v>
       </c>
       <c r="R4" t="n">
-        <v>6816140</v>
+        <v>6816448</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,6 +973,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -989,48 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809779</v>
+        <v>129809713</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stuplav sotbo, Dlr</t>
+          <t>Tretåig hackspett 1, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473743</v>
+        <v>473665</v>
       </c>
       <c r="R5" t="n">
-        <v>6816448</v>
+        <v>6816140</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,21 +1085,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1208,27 +1208,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129809770</v>
+        <v>129809630</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>58377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1237,24 +1237,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tretå 2 Sotbo , Dlr</t>
+          <t>Tallbit, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473875</v>
+        <v>473785</v>
       </c>
       <c r="R7" t="n">
-        <v>6816623</v>
+        <v>6816297</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,11 +1279,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,27 +1305,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129809630</v>
+        <v>129809770</v>
       </c>
       <c r="B8" t="n">
-        <v>58377</v>
+        <v>57741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1344,19 +1334,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tallbit, Dlr</t>
+          <t>Tretå 2 Sotbo , Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473785</v>
+        <v>473875</v>
       </c>
       <c r="R8" t="n">
-        <v>6816297</v>
+        <v>6816623</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,6 +1381,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129321045</v>
+        <v>129809713</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sillmäckö, Dlr</t>
+          <t>Tretåig hackspett 1, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473812</v>
+        <v>473665</v>
       </c>
       <c r="R2" t="n">
-        <v>6816606</v>
+        <v>6816140</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,34 +740,19 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall 2,5-3 m upp.</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -787,56 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129809725</v>
+        <v>129809779</v>
       </c>
       <c r="B3" t="n">
-        <v>91661</v>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granticka 1, Dlr</t>
+          <t>Stuplav sotbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473713</v>
+        <v>473743</v>
       </c>
       <c r="R3" t="n">
-        <v>6816382</v>
+        <v>6816448</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,6 +853,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -892,48 +884,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129809779</v>
+        <v>129321045</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stuplav sotbo, Dlr</t>
+          <t>Sillmäckö, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473743</v>
+        <v>473812</v>
       </c>
       <c r="R4" t="n">
-        <v>6816448</v>
+        <v>6816606</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,57 +961,57 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall 2,5-3 m upp.</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129809713</v>
+        <v>129809703</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,24 +1019,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tretåig hackspett 1, Dlr</t>
@@ -1075,6 +1084,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhackad gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129809703</v>
+        <v>129809770</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,17 +1151,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett 1, Dlr</t>
+          <t>Tretå 2 Sotbo , Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473665</v>
+        <v>473875</v>
       </c>
       <c r="R6" t="n">
-        <v>6816140</v>
+        <v>6816623</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,11 +1225,11 @@
         <v>129809630</v>
       </c>
       <c r="B7" t="n">
-        <v>58377</v>
+        <v>58592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1302,113 +1316,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>129809770</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Tretå 2 Sotbo , Dlr</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>473875</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6816623</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhackad gran</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967490</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969948</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809713</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134958177</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971429</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959837</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965591</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134966226</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134963215</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970140</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967272</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970366</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809779</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959230</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134969190</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2460,6 +2550,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129321045</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809703</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2674,6 +2774,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809770</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2776,6 +2881,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134956853</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2878,6 +2988,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957269</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2975,6 +3090,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129809630</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3072,6 +3192,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959229</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3173,8 +3298,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 49516-2025 artfynd.xlsx
+++ b/artfynd/A 49516-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134967490</v>
       </c>
       <c r="B2" t="n">
-        <v>92199</v>
+        <v>92241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134969948</v>
       </c>
       <c r="B3" t="n">
-        <v>93309</v>
+        <v>93351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>134957270</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>134958177</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>134969188</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>134971429</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>134959837</v>
       </c>
       <c r="B9" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>134965591</v>
       </c>
       <c r="B10" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>134966226</v>
       </c>
       <c r="B11" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>134963215</v>
       </c>
       <c r="B12" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>134970140</v>
       </c>
       <c r="B13" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>134967272</v>
       </c>
       <c r="B14" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>134970366</v>
       </c>
       <c r="B15" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>134959230</v>
       </c>
       <c r="B17" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>134969190</v>
       </c>
       <c r="B18" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>134956853</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>134957269</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>134959229</v>
       </c>
       <c r="B25" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>134968330</v>
       </c>
       <c r="B26" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
